--- a/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,52; 74,71</t>
+          <t>63,3; 74,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,29; 73,89</t>
+          <t>62,97; 73,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,15; 72,96</t>
+          <t>64,8; 72,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,52; 76,12</t>
+          <t>64,84; 76,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,38; 84,69</t>
+          <t>75,2; 84,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,71; 78,45</t>
+          <t>70,62; 78,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,47; 82,97</t>
+          <t>71,89; 83,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,42; 88,22</t>
+          <t>74,77; 88,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,02; 83,24</t>
+          <t>74,7; 83,57</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,51; 82,31</t>
+          <t>72,91; 82,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,39; 93,87</t>
+          <t>74,37; 92,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,93; 90,03</t>
+          <t>75,88; 89,83</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,94; 87,57</t>
+          <t>76,98; 87,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,33; 85,11</t>
+          <t>55,79; 85,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,3; 84,5</t>
+          <t>64,56; 84,53</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52,46; 82,24</t>
+          <t>49,37; 82,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76,49; 84,54</t>
+          <t>76,08; 84,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,32; 82,64</t>
+          <t>72,66; 82,37</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,99; 77,66</t>
+          <t>73,01; 77,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,69; 86,07</t>
+          <t>75,44; 85,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,17; 81,44</t>
+          <t>75,41; 81,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>168184; 197818</t>
+          <t>167596; 197423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>135711; 158452</t>
+          <t>135032; 157141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312229; 349632</t>
+          <t>310514; 348699</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>166861; 196864</t>
+          <t>167682; 197614</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138831; 155991</t>
+          <t>138504; 155916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313094; 347361</t>
+          <t>312708; 348046</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163673; 187383</t>
+          <t>162369; 188391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61497; 71935</t>
+          <t>60966; 71918</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227528; 255881</t>
+          <t>229629; 256883</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>390574; 437360</t>
+          <t>387371; 436018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>443383; 559446</t>
+          <t>443228; 554077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>855933; 1014908</t>
+          <t>855360; 1012674</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>177044; 201517</t>
+          <t>177133; 201417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213819; 328932</t>
+          <t>215592; 329638</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>408804; 521009</t>
+          <t>398052; 521168</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58038; 90993</t>
+          <t>54620; 90853</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>316135; 349402</t>
+          <t>314446; 347873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>384125; 433000</t>
+          <t>380688; 431545</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1183338; 1259146</t>
+          <t>1183793; 1262388</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1419959; 1614582</t>
+          <t>1415164; 1599798</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2628903; 2848305</t>
+          <t>2637306; 2856040</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,3; 74,56</t>
+          <t>62,21; 73,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,97; 73,28</t>
+          <t>62,3; 73,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,8; 72,76</t>
+          <t>64,12; 71,89</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,84; 76,41</t>
+          <t>63,6; 75,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,2; 84,65</t>
+          <t>74,75; 84,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,62; 78,6</t>
+          <t>70,15; 77,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,89; 83,41</t>
+          <t>72,17; 83,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,77; 88,2</t>
+          <t>75,08; 87,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,7; 83,57</t>
+          <t>74,95; 83,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,91; 82,06</t>
+          <t>74,71; 82,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,37; 92,97</t>
+          <t>72,62; 79,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,88; 89,83</t>
+          <t>74,68; 80,31</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,98; 87,53</t>
+          <t>77,29; 86,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,79; 85,3</t>
+          <t>80,75; 86,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,56; 84,53</t>
+          <t>80,83; 86,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49,37; 82,12</t>
+          <t>54,16; 82,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76,08; 84,17</t>
+          <t>77,54; 84,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,66; 82,37</t>
+          <t>74,56; 82,79</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,01; 77,86</t>
+          <t>73,32; 77,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,44; 85,28</t>
+          <t>77,27; 80,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,41; 81,67</t>
+          <t>76,1; 78,84</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>183376</t>
+          <t>195092</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>147470</t>
+          <t>160109</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330845</t>
+          <t>355201</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>167596; 197423</t>
+          <t>177475; 209211</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>135032; 157141</t>
+          <t>146601; 171763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310514; 348699</t>
+          <t>333815; 374260</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>182831</t>
+          <t>190128</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>148150</t>
+          <t>161721</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330981</t>
+          <t>351849</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>167682; 197614</t>
+          <t>173050; 204407</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138504; 155916</t>
+          <t>151129; 170164</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>312708; 348046</t>
+          <t>332725; 369530</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67116</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243802</t>
+          <t>274565</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>162369; 188391</t>
+          <t>181309; 209851</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60966; 71918</t>
+          <t>69709; 81448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229629; 256883</t>
+          <t>257867; 287313</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>415595</t>
+          <t>449628</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>500042</t>
+          <t>326314</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915638</t>
+          <t>775941</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>387371; 436018</t>
+          <t>425089; 470376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>443228; 554077</t>
+          <t>310460; 340418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>855360; 1012674</t>
+          <t>744150; 800243</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>225531</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>298258</t>
+          <t>337414</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488254</t>
+          <t>562945</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>177133; 201417</t>
+          <t>210694; 236498</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215592; 329638</t>
+          <t>323635; 348135</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>398052; 521168</t>
+          <t>544304; 579900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>76179</t>
+          <t>79205</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>334015</t>
+          <t>370785</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410193</t>
+          <t>449989</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54620; 90853</t>
+          <t>61190; 93283</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>314446; 347873</t>
+          <t>353531; 385990</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>380688; 431545</t>
+          <t>424151; 470954</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1224663</t>
+          <t>1337716</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1495050</t>
+          <t>1432775</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2719714</t>
+          <t>2770490</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1183793; 1262388</t>
+          <t>1292722; 1372319</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1415164; 1599798</t>
+          <t>1402155; 1461856</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2637306; 2856040</t>
+          <t>2722696; 2820565</t>
         </is>
       </c>
     </row>
